--- a/data/trans_orig/IQ3005_MoAR-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Edad-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer huevo</t>
+          <t>Menores según la edad en meses en la que empezaron a comer huevo (tasa de respuesta: 48,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,54 +677,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,37; 11,95</t>
+          <t>10,46; 11,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,8; 11,99</t>
+          <t>10,76; 12,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,18; 10,46</t>
+          <t>9,14; 10,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 11,81</t>
+          <t>10,7; 11,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,68; 11,63</t>
+          <t>10,68; 11,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,71; 9,99</t>
+          <t>8,7; 9,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,81; 11,68</t>
+          <t>10,78; 11,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,87; 11,62</t>
+          <t>10,9; 11,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,94</t>
+          <t>9,05; 9,99</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -734,47 +734,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,21</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,3</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,71</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,28</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,14</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,35</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,25</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,22</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,53</t>
         </is>
       </c>
     </row>
@@ -787,398 +787,65 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,46; 11,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,76; 12,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,14; 10,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,7; 11,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,68; 11,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,7; 9,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,78; 11,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,9; 11,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,05; 9,99</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>11,21</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11,3</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,28</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,14</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,35</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,25</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11,22</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>10,37; 11,95</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10,8; 11,99</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9,18; 10,46</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10,65; 11,81</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10,68; 11,63</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,71; 9,99</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,81; 11,68</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10,87; 11,62</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9,06; 9,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="6">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IQ3005_MoAR-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Edad-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,46; 11,95</t>
+          <t>10,38; 11,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,76; 12,13</t>
+          <t>10,8; 12,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,14; 10,35</t>
+          <t>9,12; 10,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,7; 11,81</t>
+          <t>10,67; 11,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,68; 11,68</t>
+          <t>10,69; 11,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,7; 9,99</t>
+          <t>8,73; 10,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,78; 11,73</t>
+          <t>10,77; 11,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,9; 11,72</t>
+          <t>10,86; 11,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,99</t>
+          <t>9,11; 9,98</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,46; 11,95</t>
+          <t>10,38; 11,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,76; 12,13</t>
+          <t>10,8; 12,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,14; 10,35</t>
+          <t>9,12; 10,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,7; 11,81</t>
+          <t>10,67; 11,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,68; 11,68</t>
+          <t>10,69; 11,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,7; 9,99</t>
+          <t>8,73; 10,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,78; 11,73</t>
+          <t>10,77; 11,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,9; 11,72</t>
+          <t>10,86; 11,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,99</t>
+          <t>9,11; 9,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3005_MoAR-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Edad-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,35</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>11,21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11,3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,71</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,28</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,14</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,38; 11,96</t>
+          <t>10,65; 11,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,8; 12,08</t>
+          <t>10,68; 11,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,12; 10,29</t>
+          <t>8,71; 9,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 11,81</t>
+          <t>10,37; 11,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,69; 11,62</t>
+          <t>10,8; 11,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,73; 10,02</t>
+          <t>9,18; 10,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,77; 11,69</t>
+          <t>10,81; 11,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,86; 11,66</t>
+          <t>10,87; 11,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,11; 9,98</t>
+          <t>9,06; 9,94</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,28</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,14</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,35</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>11,21</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>11,3</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,71</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,28</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,14</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,35</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,38; 11,96</t>
+          <t>10,65; 11,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,8; 12,08</t>
+          <t>10,68; 11,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 10,29</t>
+          <t>8,71; 9,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,67; 11,81</t>
+          <t>10,37; 11,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,69; 11,62</t>
+          <t>10,8; 11,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,73; 10,02</t>
+          <t>9,18; 10,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,77; 11,69</t>
+          <t>10,81; 11,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 11,66</t>
+          <t>10,87; 11,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,11; 9,98</t>
+          <t>9,06; 9,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3005_MoAR-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer huevo (tasa de respuesta: 48,37%)</t>
+          <t>Edad media en meses a la que los menores empezaron a comer huevo (tasa de respuesta: 48,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,229 +627,117 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>11,28</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11,14</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,35</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,21</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,25</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11,22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>11.28417301559822</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>11.14422777139552</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9.34668281645331</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>11.20630757442294</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>11.30324518534518</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>9.7089233786826</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>11.24963825833229</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>11.22417108368449</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>9.525522734041665</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>10,65; 11,81</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10,68; 11,63</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8,71; 9,99</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10,37; 11,95</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,8; 11,99</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,18; 10,46</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,81; 11,68</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10,87; 11,62</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9,06; 9,94</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>10.64809667044202</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>10.67999182304633</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>8.71068908156084</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>10.37498581962022</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>10.80123575423183</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>9.18391918169867</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>10.80931831765325</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>10.87275952914075</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>9.062670232824527</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>11,28</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11,14</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9,35</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,21</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,3</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,25</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11,22</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.80988921387442</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>11.62985829075116</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.985202220271852</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>11.94753713746618</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>11.99059437484276</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>10.45868568067961</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>11.67686966790702</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>11.62135942144971</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>9.939004192378006</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>10,65; 11,81</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10,68; 11,63</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8,71; 9,99</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10,37; 11,95</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10,8; 11,99</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,18; 10,46</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,81; 11,68</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10,87; 11,62</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9,06; 9,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A4:A6"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
